--- a/tiktok-analytics/data/20260601/订单收入大表_20260601_20260604_002133.xlsx
+++ b/tiktok-analytics/data/20260601/订单收入大表_20260601_20260604_002133.xlsx
@@ -8020,10 +8020,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -8039,6 +8035,10 @@
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -8397,17 +8397,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="36" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -8638,56 +8638,56 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15">
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="11" t="s">
         <v>2591</v>
       </c>
-      <c r="C12" s="14"/>
+      <c r="C12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="15">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>2592</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>2593</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>2594</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>2595</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>2596</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>2597</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15">
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>2598</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="14" t="s">
         <v>2599</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15">
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>2600</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="14" t="s">
         <v>2601</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="15">
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>2602</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="15">
         <v>7.4899999999999994E-2</v>
       </c>
     </row>
